--- a/src/main/resources/grantorUserRegistration_Field_Values.xlsx
+++ b/src/main/resources/grantorUserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3B5414-A4C8-43E3-B20E-B445D01FEE4C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1D2192-3E84-4C4E-83A8-2DA48E601BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SubjectMatterExpertDetails" sheetId="15" r:id="rId1"/>
@@ -172,57 +172,27 @@
     <t>IND: INDIA</t>
   </si>
   <si>
-    <t>fieldPrimaryRepPrefix__c</t>
-  </si>
-  <si>
     <t>Mr.</t>
   </si>
   <si>
-    <t>fieldPrimaryRepFirstName__c</t>
-  </si>
-  <si>
     <t>Automation</t>
   </si>
   <si>
-    <t>fieldPrimaryRepMiddleName__c</t>
-  </si>
-  <si>
     <t>Ned</t>
   </si>
   <si>
-    <t>fieldPrimaryRepLastName__c</t>
-  </si>
-  <si>
     <t>User</t>
   </si>
   <si>
-    <t>fieldPreferredName__c</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>fieldPreferredPronoun__c</t>
-  </si>
-  <si>
     <t>He/Him</t>
   </si>
   <si>
-    <t>fieldPrimaryRepTitle__c</t>
-  </si>
-  <si>
     <t>Automation Primary Representative</t>
   </si>
   <si>
-    <t>fieldSigningAuthority__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepEmail__c</t>
-  </si>
-  <si>
-    <t>fieldApplicantOrganizationPhone__c</t>
-  </si>
-  <si>
     <t>fieldExternalReviewerPrefix__c</t>
   </si>
   <si>
@@ -238,40 +208,70 @@
     <t>fieldExternalReviewerAddress1__c</t>
   </si>
   <si>
-    <t>fieldExternalReviewerCity__c</t>
-  </si>
-  <si>
-    <t>fieldStateDropdownList__c</t>
-  </si>
-  <si>
     <t>FL</t>
   </si>
   <si>
-    <t>fieldExternalReviewerZipCode__c</t>
-  </si>
-  <si>
-    <t>fieldAffiliatedInstitution__c</t>
-  </si>
-  <si>
-    <t>fieldExternalReviewerPhone__c</t>
-  </si>
-  <si>
-    <t>fieldExternalReviewerEducation__c</t>
-  </si>
-  <si>
-    <t>fieldExternalReviewerProfileDescription__c</t>
-  </si>
-  <si>
     <t>I am automation QA</t>
   </si>
   <si>
-    <t>fieldPrimaryAreaOfExpertisePicklist__c</t>
-  </si>
-  <si>
     <t>Quality Assurance</t>
   </si>
   <si>
-    <t>fieldPrimaryAreaOfExpertise__c</t>
+    <t>ExternalReviewerCity__c</t>
+  </si>
+  <si>
+    <t>StateDropdownList__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerZipCode__c</t>
+  </si>
+  <si>
+    <t>AffiliatedInstitution__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerPhone__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerEducation__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerProfileDescription__c</t>
+  </si>
+  <si>
+    <t>PrimaryAreaOfExpertisePicklist__c</t>
+  </si>
+  <si>
+    <t>PrimaryAreaOfExpertise__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepPrefix__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepFirstName__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepMiddleName__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepLastName__c</t>
+  </si>
+  <si>
+    <t>PreferredName__c</t>
+  </si>
+  <si>
+    <t>PreferredPronoun__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepTitle__c</t>
+  </si>
+  <si>
+    <t>SigningAuthority__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepEmail__c</t>
+  </si>
+  <si>
+    <t>ApplicantOrganizationPhone__c</t>
   </si>
 </sst>
 </file>
@@ -389,9 +389,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -678,14 +678,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C91047-BCF7-48FB-B48B-2C6C45D92926}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -696,147 +696,147 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>66</v>
+      <c r="B6" t="s">
+        <v>59</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>67</v>
+      <c r="B7" t="s">
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>69</v>
+      <c r="B8" t="s">
+        <v>61</v>
       </c>
       <c r="C8">
         <v>20171</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>70</v>
+      <c r="B9" t="s">
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>71</v>
+      <c r="B10" t="s">
+        <v>63</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>72</v>
+      <c r="B11" t="s">
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>73</v>
+      <c r="B12" t="s">
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>77</v>
+      <c r="B14" t="s">
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -848,13 +848,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5343F989-BED4-4C3F-AE8F-330830F9208D}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -865,7 +865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -876,7 +876,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -887,7 +887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -898,7 +898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -909,7 +909,7 @@
         <v>20171</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -920,7 +920,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -943,13 +943,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B216D1F-84FF-4062-A939-3C635B054F5E}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -960,7 +960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -971,7 +971,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -982,7 +982,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -1002,13 +1002,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C7FB28-3C46-41CD-B1C8-5ACD5AA83D43}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
@@ -1083,13 +1083,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B080C06C-48BE-4956-AB6C-FA9A46DD80B4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -1153,13 +1153,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44E55028-70E0-4DC2-93F0-398F08D85BA5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>987654321</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
@@ -1234,13 +1234,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCE78A5-F6A7-4E3D-A256-8FF61363066F}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>20171</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1329,14 +1329,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4BF3096-62C1-489E-B677-AEC71181CA96}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1347,111 +1347,111 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="11" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="12" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="11" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="12" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="11" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="12" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>27</v>
@@ -1469,13 +1469,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="32.46484375" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" customWidth="1"/>
+    <col min="3" max="3" width="51.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
@@ -1564,13 +1564,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A00A2F9B-1F15-474D-9DD4-993171530508}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.46484375" customWidth="1"/>
-    <col min="3" max="3" width="17.796875" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -1600,12 +1600,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05EFA198-FBA1-4B9A-B3E9-28166FF18612}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1636,12 +1636,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1A298F-7844-48D1-98DD-53D7D86DE791}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1671,12 +1671,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C6C8DD-009D-425E-9B69-09D5E0ACEE9D}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.46484375" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1706,13 +1706,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2F0CAC-30A4-45BD-AE27-07806349BD24}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.53125" customWidth="1"/>
-    <col min="3" max="3" width="19.19921875" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/grantorUserRegistration_Field_Values.xlsx
+++ b/src/main/resources/grantorUserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Santosh\REIProject\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1D2192-3E84-4C4E-83A8-2DA48E601BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84933BDB-E833-4DEC-9492-F44535DE1933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SubjectMatterExpertDetails" sheetId="15" r:id="rId1"/>
@@ -193,21 +193,9 @@
     <t>Automation Primary Representative</t>
   </si>
   <si>
-    <t>fieldExternalReviewerPrefix__c</t>
-  </si>
-  <si>
-    <t>fieldExternalReviewerFirstName__c</t>
-  </si>
-  <si>
     <t>Automation SME</t>
   </si>
   <si>
-    <t>fieldExternalReviewerLastName__c</t>
-  </si>
-  <si>
-    <t>fieldExternalReviewerAddress1__c</t>
-  </si>
-  <si>
     <t>FL</t>
   </si>
   <si>
@@ -272,6 +260,18 @@
   </si>
   <si>
     <t>ApplicantOrganizationPhone__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerPrefix__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerFirstName__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerLastName__c</t>
+  </si>
+  <si>
+    <t>ExternalReviewerAddress1__c</t>
   </si>
 </sst>
 </file>
@@ -701,7 +701,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>44</v>
@@ -712,10 +712,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -723,7 +723,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>47</v>
@@ -734,7 +734,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
@@ -745,7 +745,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
@@ -756,10 +756,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -767,7 +767,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C8">
         <v>20171</v>
@@ -778,7 +778,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
@@ -789,7 +789,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
@@ -800,7 +800,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
         <v>45</v>
@@ -811,10 +811,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -822,10 +822,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -833,7 +833,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
         <v>48</v>
@@ -1352,7 +1352,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>44</v>
@@ -1363,7 +1363,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>45</v>
@@ -1374,7 +1374,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>46</v>
@@ -1385,7 +1385,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>47</v>
@@ -1396,7 +1396,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>48</v>
@@ -1407,7 +1407,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>49</v>
@@ -1418,7 +1418,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>50</v>
@@ -1429,7 +1429,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>6</v>
@@ -1440,7 +1440,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>25</v>
@@ -1451,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>27</v>
